--- a/data/gravel/Brodie Romax Titanium 2025.xlsx
+++ b/data/gravel/Brodie Romax Titanium 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90862F5-840C-9E42-BCD0-B93D65AA9323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C154F01-8DFD-AF4C-93B3-37A2794276B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -717,14 +717,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
     <col min="3" max="16384" width="10.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -732,7 +732,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -740,7 +740,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -748,7 +748,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -756,7 +756,7 @@
         <v>45988</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -764,7 +764,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>105</v>
       </c>
@@ -777,7 +777,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -793,7 +793,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -816,7 +816,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -839,7 +839,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -862,7 +862,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -885,7 +885,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -908,7 +908,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -931,7 +931,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -954,7 +954,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -962,22 +962,42 @@
         <v>102</v>
       </c>
       <c r="C15" s="1">
+        <f>H15*-1</f>
+        <v>72</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" ref="D15:G15" si="0">I15*-1</f>
+        <v>72</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="H15" s="1">
         <v>-72</v>
       </c>
-      <c r="D15" s="1">
+      <c r="I15" s="1">
         <v>-72</v>
       </c>
-      <c r="E15" s="1">
+      <c r="J15" s="1">
         <v>-72</v>
       </c>
-      <c r="F15" s="1">
+      <c r="K15" s="1">
         <v>-72</v>
       </c>
-      <c r="G15" s="1">
+      <c r="L15" s="1">
         <v>-72</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,19 +1223,19 @@
         <v>160.02000000000001</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" ref="D30:F31" si="0">2.54*D32</f>
+        <f t="shared" ref="D30:F31" si="1">2.54*D32</f>
         <v>165.1</v>
       </c>
       <c r="E30" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>170.18</v>
       </c>
       <c r="F30" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>175.26</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" ref="G30" si="1">2.54*G32</f>
+        <f t="shared" ref="G30" si="2">2.54*G32</f>
         <v>180.34</v>
       </c>
     </row>
@@ -1231,19 +1251,19 @@
         <v>167.64000000000001</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>172.72</v>
       </c>
       <c r="E31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>177.8</v>
       </c>
       <c r="F31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>182.88</v>
       </c>
       <c r="G31" s="1">
-        <f t="shared" ref="G31" si="2">2.54*G33</f>
+        <f t="shared" ref="G31" si="3">2.54*G33</f>
         <v>193.04</v>
       </c>
     </row>
